--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-13T01:40:58Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-13T21:56:37Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-13T21:56:37Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-14T01:59:05Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-14T01:59:05Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-14T07:25:05Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-14T07:25:05Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-14T19:43:42Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-14T19:43:42Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-14T22:52:20Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-14T22:52:20Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-15T01:04:40Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-15T01:04:40Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-15T06:55:19Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-15T06:55:19Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-15T12:20:48Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-15T12:20:48Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-15T17:24:58Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-15T17:24:58Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-15T20:33:12Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-15T20:33:12Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-15T23:16:45Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-15T23:16:45Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-16T02:00:25Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-16T02:00:25Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-16T07:01:08Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-16T07:01:08Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-16T12:21:03Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-16T12:21:03Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-16T17:25:46Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-16T17:25:46Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-16T20:36:54Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-16T20:36:54Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-16T23:24:38Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-16T23:24:38Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-17T02:01:03Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-17T02:01:03Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-17T07:12:49Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-17T07:12:49Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-17T12:54:46Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-17T12:54:46Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-17T17:24:49Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-17T17:24:49Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-17T20:43:13Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-17T20:43:13Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-17T23:11:58Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-17T23:11:58Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-18T01:50:54Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-18T01:50:54Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-18T06:51:23Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-18T06:51:23Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-18T12:01:10Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-18T12:01:10Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-18T15:29:14Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-18T15:29:14Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-18T18:49:47Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-18T18:49:47Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-18T21:26:25Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-18T21:26:25Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-19T01:59:32Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-19T01:59:32Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-20T02:01:09Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-20T02:01:09Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-20T16:41:07Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-20T16:41:07Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-20T22:05:51Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-20T22:05:51Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-20T23:51:05Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-20T23:51:05Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-21T01:58:38Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-21T01:58:38Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-21T07:28:07Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-21T07:28:07Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-21T19:50:11Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-21T19:50:11Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-21T22:59:58Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-21T22:59:58Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-22T01:21:26Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-22T01:21:26Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-22T07:00:48Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-22T07:00:48Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-22T12:17:43Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-22T12:17:43Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-22T17:30:00Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-22T17:30:00Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-22T23:25:41Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-22T23:25:41Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-23T02:06:35Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-23T02:06:35Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-23T07:32:40Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-23T07:32:40Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-23T13:10:16Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-23T13:10:16Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-23T18:06:43Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-23T18:06:43Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-23T21:58:35Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-23T21:58:35Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-24T00:08:17Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-24T00:08:17Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-24T05:40:28Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-24T05:40:28Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-24T22:52:36Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-24T22:52:36Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-25T05:44:51Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-25T05:44:51Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-25T15:42:05Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-25T15:42:05Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-25T19:39:58Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-25T19:39:58Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-25T22:55:39Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-25T22:55:39Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-26T01:06:39Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-26T01:06:39Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-26T05:59:06Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-26T05:59:06Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-27T03:13:15Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-27T03:13:15Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-27T09:38:54Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-27T09:38:54Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-28T14:46:46Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-28T14:46:46Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-29T06:26:29Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-29T06:26:29Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-29T13:35:05Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-29T13:35:05Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-29T19:05:09Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-29T19:05:09Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-29T22:54:16Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-29T22:54:16Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-30T01:49:38Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-30T01:49:38Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-30T14:26:35Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-30T14:26:35Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-30T19:48:42Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-30T19:48:42Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-30T23:21:56Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-09-30T23:21:56Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-01T02:43:13Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-01T02:43:13Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-01T09:38:59Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-01T09:38:59Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-02T14:19:36Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-02T14:19:36Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-02T19:42:47Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-02T19:42:47Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-02T23:24:50Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-02T23:24:50Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-03T02:38:51Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-03T02:38:51Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-03T08:46:21Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-03T08:46:21Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-03T14:07:02Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-03T14:07:02Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-03T17:51:52Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-03T17:51:52Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-03T20:24:23Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-03T20:24:23Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-03T23:32:24Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-03T23:32:24Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-04T18:58:23Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-04T18:58:23Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-06T02:41:50Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-06T02:41:50Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-08T00:38:15Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-08T00:38:15Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-08T14:14:13Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-08T14:14:13Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-09T00:51:09Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-09T00:51:09Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-09T13:59:38Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-09T13:59:38Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-09T23:44:39Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-09T23:44:39Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-10T03:05:54Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-10T03:05:54Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-11T09:26:49Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-11T09:26:49Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-13T01:48:09Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-13T01:48:09Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-13T16:40:05Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-13T16:40:05Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-13T21:36:41Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-13T21:36:41Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-14T05:38:33Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-14T05:38:33Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-14T19:52:17Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-14T19:52:17Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-14T22:50:38Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-14T22:50:38Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-15T01:05:10Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-15T01:05:10Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-15T06:40:59Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-15T06:40:59Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-15T12:19:59Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-15T12:19:59Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-15T17:35:06Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-15T17:35:06Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-15T23:30:54Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-15T23:30:54Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-16T01:55:51Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-16T01:55:51Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-16T19:11:21Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-16T19:11:21Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-16T22:23:47Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-16T22:23:47Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-17T00:56:06Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-17T00:56:06Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-17T05:14:06Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-17T05:14:06Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-17T09:53:28Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-17T09:53:28Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-17T13:25:55Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-17T13:25:55Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-18T15:01:33Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-18T15:01:33Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-19T20:53:33Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-19T20:53:33Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-20T00:07:48Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-20T00:07:48Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-20T03:29:33Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-20T03:29:33Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-20T14:06:16Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-20T14:06:16Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-20T18:21:06Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-20T18:21:06Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-20T22:05:48Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-20T22:05:48Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-21T00:28:58Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-21T00:28:58Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-21T05:36:13Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-21T05:36:13Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-21T10:50:57Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-21T10:50:57Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-21T15:47:14Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-21T15:47:14Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-21T19:47:48Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-21T19:47:48Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-21T22:59:38Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-21T22:59:38Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-22T06:49:22Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-22T06:49:22Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-22T12:41:33Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-22T12:41:33Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-22T17:49:26Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-22T17:49:26Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-24T02:13:24Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-24T02:13:24Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-24T07:46:40Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-24T07:46:40Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-24T12:22:11Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-24T12:22:11Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-24T16:25:49Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-24T16:25:49Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-24T19:15:37Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-24T19:15:37Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-24T22:10:14Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-24T22:10:14Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-25T00:41:36Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-25T00:41:36Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-25T05:34:50Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-25T05:34:50Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-25T18:00:12Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-25T18:00:12Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-26T05:36:48Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-26T05:36:48Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-27T18:33:01Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-27T18:33:01Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-27T22:50:35Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-27T22:50:35Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-28T02:00:14Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-28T02:00:14Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-28T23:49:00Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-28T23:49:00Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-29T03:09:39Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-29T03:09:39Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-29T17:16:42Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>

--- a/grr.xlsx
+++ b/grr.xlsx
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-29T17:16:42Z (UTC)     ·     Managed by NewcrestImage</t>
+          <t>Reporting day: 2026-08-26     ·     Generated 2026-10-31T18:12:50Z (UTC)     ·     Managed by NewcrestImage</t>
         </is>
       </c>
     </row>
